--- a/Economic modelling/Sector_Codes.xlsx
+++ b/Economic modelling/Sector_Codes.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <xr:revisionPtr revIDLastSave="210" documentId="8_{A6291557-216E-4F61-B2DF-CC8EAA566595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0BD5D99-4FAE-42CC-A21A-D69AC22589A4}"/>
   <bookViews>
@@ -2699,6 +2699,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000E4C469DA0857744B2E25B15AB61C57C" ma:contentTypeVersion="4" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="1c25419f0913852ecd46fbe082ab918c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="96a9e30f-a77c-4cdd-aa33-614d5f6400ab" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f7abe366755686eb81ebe531f7d7e046" ns3:_="">
     <xsd:import namespace="96a9e30f-a77c-4cdd-aa33-614d5f6400ab"/>
@@ -2844,12 +2850,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2860,6 +2860,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67054F28-EE8F-4706-AFFC-DD8ACC57E081}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="96a9e30f-a77c-4cdd-aa33-614d5f6400ab"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{896B14DB-450B-47EB-B79E-9979C882CC43}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2877,22 +2893,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67054F28-EE8F-4706-AFFC-DD8ACC57E081}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="96a9e30f-a77c-4cdd-aa33-614d5f6400ab"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65F434DC-50FB-438F-922B-962BA7F686B4}">
   <ds:schemaRefs>
